--- a/docs/public/exam/2019-shang-2.xlsx
+++ b/docs/public/exam/2019-shang-2.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="15">
   <si>
     <t>序号</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>公式题，需要推导。</t>
+  </si>
+  <si>
+    <t>概念题。</t>
   </si>
   <si>
     <t>D*</t>
@@ -1908,7 +1911,9 @@
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="F30" s="9"/>
     </row>
     <row r="31" ht="14.25" hidden="1" spans="1:6">
@@ -1942,7 +1947,9 @@
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E32" s="9"/>
+      <c r="E32" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="F32" s="9"/>
     </row>
     <row r="33" ht="14.25" hidden="1" spans="1:6">
@@ -2102,7 +2109,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>5</v>
@@ -2613,7 +2620,7 @@
     </row>
     <row r="78" ht="13.85" spans="1:2">
       <c r="A78" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B78" s="25">
         <f>COUNTA(B2:B74)</f>
@@ -2622,7 +2629,7 @@
     </row>
     <row r="79" ht="13.85" spans="1:3">
       <c r="A79" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B79" s="25">
         <f>COUNTIF(D4:D76,"真")</f>
@@ -2632,7 +2639,7 @@
     </row>
     <row r="80" ht="13.85" spans="1:3">
       <c r="A80" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B80" s="25">
         <f>B78-B79</f>
@@ -2642,10 +2649,10 @@
     </row>
     <row r="81" ht="13.85" spans="1:2">
       <c r="A81" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/public/exam/2019-shang-2.xlsx
+++ b/docs/public/exam/2019-shang-2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10020" windowHeight="10455"/>
+    <workbookView windowWidth="14800" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet name="2016年上半年" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="14">
   <si>
     <t>序号</t>
   </si>
@@ -787,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,9 +839,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -856,9 +853,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1403,16 +1397,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9.8141592920354" style="4"/>
-    <col min="3" max="3" width="11.7522123893805" customWidth="1"/>
-    <col min="4" max="4" width="5.1858407079646" customWidth="1"/>
-    <col min="5" max="5" width="10.2743362831858"/>
-    <col min="6" max="6" width="16.5663716814159" customWidth="1"/>
+    <col min="2" max="2" width="9.81818181818182" style="4"/>
+    <col min="3" max="3" width="11.7545454545455" customWidth="1"/>
+    <col min="4" max="4" width="5.18181818181818" customWidth="1"/>
+    <col min="5" max="5" width="10.2727272727273"/>
+    <col min="6" max="6" width="16.5636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" ht="15" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1422,7 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
     </row>
-    <row r="2" ht="14.25" hidden="1" spans="1:6">
+    <row r="2" ht="15" hidden="1" spans="1:6">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1445,7 +1439,7 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" ht="14.25" hidden="1" spans="1:6">
+    <row r="3" ht="15" hidden="1" spans="1:6">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1462,7 +1456,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="14.25" hidden="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="15" hidden="1" spans="1:6">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1478,7 +1472,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" ht="14.25" hidden="1" spans="1:6">
+    <row r="5" ht="15" hidden="1" spans="1:6">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1495,7 +1489,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:6">
+    <row r="6" s="2" customFormat="1" ht="15" hidden="1" spans="1:6">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1512,7 +1506,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
     </row>
-    <row r="7" ht="14.25" spans="1:6">
+    <row r="7" ht="15" spans="1:6">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -1527,7 +1521,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" ht="14.25" hidden="1" spans="1:6">
+    <row r="8" ht="15" hidden="1" spans="1:6">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -1543,7 +1537,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" ht="14.25" hidden="1" spans="1:6">
+    <row r="9" ht="15" hidden="1" spans="1:6">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -1560,7 +1554,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" ht="14.25" hidden="1" spans="1:6">
+    <row r="10" ht="15" hidden="1" spans="1:6">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -1577,7 +1571,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" ht="14.25" hidden="1" spans="1:6">
+    <row r="11" ht="15" hidden="1" spans="1:6">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -1594,7 +1588,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" ht="14.25" hidden="1" spans="1:6">
+    <row r="12" ht="15" hidden="1" spans="1:6">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -1611,7 +1605,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" ht="14.25" hidden="1" spans="1:6">
+    <row r="13" ht="15" hidden="1" spans="1:6">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -1627,7 +1621,7 @@
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" s="3" customFormat="1" ht="14.25" hidden="1" spans="1:6">
+    <row r="14" s="3" customFormat="1" ht="15" hidden="1" spans="1:6">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -1644,11 +1638,11 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" s="3" customFormat="1" ht="14.25" hidden="1" spans="1:6">
+    <row r="15" s="3" customFormat="1" ht="15" hidden="1" spans="1:6">
       <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="14" t="s">
@@ -1661,7 +1655,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" ht="14.25" hidden="1" spans="1:6">
+    <row r="16" ht="15" hidden="1" spans="1:6">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -1677,7 +1671,7 @@
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" ht="14.25" hidden="1" spans="1:6">
+    <row r="17" ht="15" hidden="1" spans="1:6">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -1694,11 +1688,11 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" ht="14.25" hidden="1" spans="1:6">
+    <row r="18" ht="15" hidden="1" spans="1:6">
       <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="14" t="s">
@@ -1711,11 +1705,11 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" ht="14.25" hidden="1" spans="1:6">
+    <row r="19" ht="15" hidden="1" spans="1:6">
       <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="15" t="s">
@@ -1728,7 +1722,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" ht="14.25" hidden="1" spans="1:6">
+    <row r="20" ht="15" hidden="1" spans="1:6">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -1745,7 +1739,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" ht="14.25" hidden="1" spans="1:6">
+    <row r="21" ht="15" hidden="1" spans="1:6">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -1762,7 +1756,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" ht="14.25" hidden="1" spans="1:6">
+    <row r="22" ht="15" hidden="1" spans="1:6">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -1776,43 +1770,43 @@
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" ht="14.25" hidden="1" spans="1:7">
+      <c r="F22" s="19"/>
+    </row>
+    <row r="23" ht="15" hidden="1" spans="1:7">
       <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="20" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="10" t="str">
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="F23" s="20"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" ht="14.25" hidden="1" spans="1:7">
+    <row r="24" ht="15" hidden="1" spans="1:7">
       <c r="A24" s="13">
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="10" t="str">
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="F24" s="20"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" ht="14.25" hidden="1" spans="1:7">
+    <row r="25" ht="15" hidden="1" spans="1:7">
       <c r="A25" s="13">
         <v>24</v>
       </c>
@@ -1826,10 +1820,10 @@
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="F25" s="20"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" ht="14.25" hidden="1" spans="1:6">
+    <row r="26" ht="15" hidden="1" spans="1:6">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -1845,7 +1839,7 @@
       </c>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" ht="14.25" hidden="1" spans="1:6">
+    <row r="27" ht="15" hidden="1" spans="1:6">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -1861,7 +1855,7 @@
       </c>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" ht="14.25" hidden="1" spans="1:6">
+    <row r="28" ht="15" hidden="1" spans="1:6">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -1875,9 +1869,9 @@
         <f t="shared" si="0"/>
         <v>真</v>
       </c>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" ht="14.25" hidden="1" spans="1:6">
+      <c r="F28" s="19"/>
+    </row>
+    <row r="29" ht="15" hidden="1" spans="1:6">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -1894,7 +1888,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="14.25" spans="1:6">
+    <row r="30" s="2" customFormat="1" ht="15" spans="1:6">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -1911,7 +1905,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" ht="14.25" hidden="1" spans="1:6">
+    <row r="31" ht="15" hidden="1" spans="1:6">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -1928,7 +1922,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" ht="14.25" spans="1:6">
+    <row r="32" ht="15" spans="1:6">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -1945,7 +1939,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" ht="14.25" hidden="1" spans="1:6">
+    <row r="33" ht="15" hidden="1" spans="1:6">
       <c r="A33" s="13">
         <v>32</v>
       </c>
@@ -1962,7 +1956,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" ht="14.25" hidden="1" spans="1:6">
+    <row r="34" ht="15" hidden="1" spans="1:6">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -1979,7 +1973,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" ht="14.25" hidden="1" spans="1:6">
+    <row r="35" ht="15" hidden="1" spans="1:6">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -1990,13 +1984,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="10" t="str">
-        <f t="shared" ref="D35:D66" si="1">IF(AND(B35="",C35=""),"假",IF(B35=C35,"真","假"))</f>
+        <f t="shared" ref="D35:D76" si="1">IF(AND(B35="",C35=""),"假",IF(B35=C35,"真","假"))</f>
         <v>真</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" ht="14.25" hidden="1" spans="1:6">
+    <row r="36" ht="15" hidden="1" spans="1:6">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -2013,7 +2007,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" ht="14.25" hidden="1" spans="1:6">
+    <row r="37" ht="15" hidden="1" spans="1:6">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -2030,7 +2024,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" ht="14.25" hidden="1" spans="1:6">
+    <row r="38" ht="15" hidden="1" spans="1:6">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -2047,7 +2041,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" ht="14.25" hidden="1" spans="1:6">
+    <row r="39" ht="15" hidden="1" spans="1:6">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -2063,7 +2057,7 @@
       </c>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" ht="14.25" hidden="1" spans="1:6">
+    <row r="40" ht="15" hidden="1" spans="1:6">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -2080,7 +2074,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" ht="14.25" hidden="1" spans="1:6">
+    <row r="41" ht="15" hidden="1" spans="1:6">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -2097,11 +2091,11 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" ht="14.25" spans="1:6">
-      <c r="A42" s="22">
+    <row r="42" ht="15" spans="1:6">
+      <c r="A42" s="21">
         <v>41</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="15" t="s">
@@ -2114,7 +2108,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" ht="14.25" hidden="1" spans="1:6">
+    <row r="43" ht="15" hidden="1" spans="1:6">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -2131,7 +2125,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" ht="14.25" hidden="1" spans="1:6">
+    <row r="44" ht="15" hidden="1" spans="1:6">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -2147,7 +2141,7 @@
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" ht="14.25" hidden="1" spans="1:6">
+    <row r="45" ht="15" hidden="1" spans="1:6">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -2164,7 +2158,7 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" ht="14.25" spans="1:6">
+    <row r="46" ht="15" spans="1:6">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -2181,7 +2175,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" ht="14.25" hidden="1" spans="1:6">
+    <row r="47" ht="15" hidden="1" spans="1:6">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -2198,7 +2192,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
     </row>
-    <row r="48" ht="14.25" hidden="1" spans="1:6">
+    <row r="48" ht="15" hidden="1" spans="1:6">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -2215,7 +2209,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" ht="14.25" hidden="1" spans="1:6">
+    <row r="49" ht="15" hidden="1" spans="1:6">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -2231,7 +2225,7 @@
       </c>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" ht="14.25" hidden="1" spans="1:6">
+    <row r="50" ht="15" hidden="1" spans="1:6">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -2248,7 +2242,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51" ht="14.25" spans="1:6">
+    <row r="51" ht="15" spans="1:6">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -2265,11 +2259,11 @@
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
     </row>
-    <row r="52" ht="14.25" spans="1:6">
+    <row r="52" ht="15" spans="1:6">
       <c r="A52" s="13">
         <v>51</v>
       </c>
-      <c r="B52" s="23"/>
+      <c r="B52" s="17"/>
       <c r="C52" s="15"/>
       <c r="D52" s="10" t="str">
         <f t="shared" si="1"/>
@@ -2278,11 +2272,11 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53" ht="14.25" spans="1:6">
+    <row r="53" ht="15" spans="1:6">
       <c r="A53" s="13">
         <v>52</v>
       </c>
-      <c r="B53" s="24"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="15"/>
       <c r="D53" s="10" t="str">
         <f t="shared" si="1"/>
@@ -2291,7 +2285,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
     </row>
-    <row r="54" ht="14.25" spans="1:6">
+    <row r="54" ht="15" spans="1:6">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -2304,7 +2298,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
-    <row r="55" ht="14.25" spans="1:6">
+    <row r="55" ht="15" spans="1:6">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -2317,7 +2311,7 @@
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
     </row>
-    <row r="56" ht="14.25" spans="1:6">
+    <row r="56" ht="15" spans="1:6">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -2330,14 +2324,16 @@
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
     </row>
-    <row r="57" ht="14.25" spans="1:6">
+    <row r="57" ht="15" spans="1:6">
       <c r="A57" s="13">
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="15"/>
+      <c r="C57" s="15" t="s">
+        <v>6</v>
+      </c>
       <c r="D57" s="10" t="str">
         <f t="shared" si="1"/>
         <v>假</v>
@@ -2345,7 +2341,7 @@
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
     </row>
-    <row r="58" ht="14.25" spans="1:6">
+    <row r="58" ht="15" spans="1:6">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -2371,7 +2367,7 @@
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
     </row>
-    <row r="60" ht="14.25" spans="1:6">
+    <row r="60" ht="15" spans="1:6">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -2384,7 +2380,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
     </row>
-    <row r="61" ht="14.25" spans="1:6">
+    <row r="61" ht="15" spans="1:6">
       <c r="A61" s="13">
         <v>60</v>
       </c>
@@ -2397,7 +2393,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
     </row>
-    <row r="62" ht="14.25" spans="1:6">
+    <row r="62" ht="15" spans="1:6">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -2410,7 +2406,7 @@
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
     </row>
-    <row r="63" ht="14.25" spans="1:6">
+    <row r="63" ht="15" spans="1:6">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -2423,7 +2419,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
     </row>
-    <row r="64" ht="14.25" spans="1:6">
+    <row r="64" ht="15" spans="1:6">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -2436,7 +2432,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
     </row>
-    <row r="65" ht="14.25" spans="1:6">
+    <row r="65" ht="15" spans="1:6">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -2449,7 +2445,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
     </row>
-    <row r="66" ht="14.25" spans="1:6">
+    <row r="66" ht="15" spans="1:6">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -2461,7 +2457,7 @@
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
     </row>
-    <row r="67" s="2" customFormat="1" ht="14.25" spans="1:6">
+    <row r="67" s="2" customFormat="1" ht="15" spans="1:6">
       <c r="A67" s="13">
         <v>66</v>
       </c>
@@ -2472,13 +2468,13 @@
         <v>6</v>
       </c>
       <c r="D67" s="10" t="str">
-        <f>IF(AND(B67="",C67=""),"假",IF(B67=C67,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
     </row>
-    <row r="68" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:6">
+    <row r="68" s="2" customFormat="1" ht="15" hidden="1" spans="1:6">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -2489,13 +2485,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="10" t="str">
-        <f>IF(AND(B68="",C68=""),"假",IF(B68=C68,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>真</v>
       </c>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
     </row>
-    <row r="69" ht="14.25" hidden="1" spans="1:6">
+    <row r="69" ht="15" hidden="1" spans="1:6">
       <c r="A69" s="13">
         <v>68</v>
       </c>
@@ -2506,13 +2502,13 @@
         <v>6</v>
       </c>
       <c r="D69" s="10" t="str">
-        <f>IF(AND(B69="",C69=""),"假",IF(B69=C69,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>真</v>
       </c>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
     </row>
-    <row r="70" ht="14.25" hidden="1" spans="1:6">
+    <row r="70" ht="15" hidden="1" spans="1:6">
       <c r="A70" s="13">
         <v>69</v>
       </c>
@@ -2523,13 +2519,13 @@
         <v>4</v>
       </c>
       <c r="D70" s="10" t="str">
-        <f>IF(AND(B70="",C70=""),"假",IF(B70=C70,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>真</v>
       </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
     </row>
-    <row r="71" ht="14.25" hidden="1" spans="1:6">
+    <row r="71" ht="15" hidden="1" spans="1:6">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -2540,120 +2536,120 @@
         <v>4</v>
       </c>
       <c r="D71" s="10" t="str">
-        <f>IF(AND(B71="",C71=""),"假",IF(B71=C71,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>真</v>
       </c>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" ht="14.25" spans="1:6">
+    <row r="72" ht="15" spans="1:6">
       <c r="A72" s="13">
         <v>71</v>
       </c>
       <c r="B72" s="13"/>
       <c r="C72" s="15"/>
       <c r="D72" s="10" t="str">
-        <f>IF(AND(B72="",C72=""),"假",IF(B72=C72,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
     </row>
-    <row r="73" ht="14.25" spans="1:6">
+    <row r="73" ht="15" spans="1:6">
       <c r="A73" s="13">
         <v>72</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="15"/>
       <c r="D73" s="10" t="str">
-        <f>IF(AND(B73="",C73=""),"假",IF(B73=C73,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" ht="14.25" spans="1:6">
+    <row r="74" ht="15" spans="1:6">
       <c r="A74" s="13">
         <v>73</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="15"/>
       <c r="D74" s="10" t="str">
-        <f>IF(AND(B74="",C74=""),"假",IF(B74=C74,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
     </row>
-    <row r="75" ht="14.25" spans="1:6">
+    <row r="75" ht="15" spans="1:6">
       <c r="A75" s="13">
         <v>74</v>
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="15"/>
       <c r="D75" s="10" t="str">
-        <f>IF(AND(B75="",C75=""),"假",IF(B75=C75,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
     </row>
-    <row r="76" ht="14.25" spans="1:6">
+    <row r="76" ht="15" spans="1:6">
       <c r="A76" s="13">
         <v>75</v>
       </c>
       <c r="B76" s="13"/>
       <c r="C76" s="15"/>
       <c r="D76" s="10" t="str">
-        <f>IF(AND(B76="",C76=""),"假",IF(B76=C76,"真","假"))</f>
+        <f t="shared" si="1"/>
         <v>假</v>
       </c>
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
     </row>
-    <row r="78" ht="13.85" spans="1:2">
+    <row r="78" ht="14.5" spans="1:2">
       <c r="A78" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B78" s="25">
+      <c r="B78" s="23">
         <f>COUNTA(B2:B74)</f>
         <v>55</v>
       </c>
     </row>
-    <row r="79" ht="13.85" spans="1:3">
+    <row r="79" ht="14.5" spans="1:3">
       <c r="A79" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B79" s="23">
         <f>COUNTIF(D4:D76,"真")</f>
         <v>46</v>
       </c>
-      <c r="C79" s="26"/>
-    </row>
-    <row r="80" ht="13.85" spans="1:3">
+      <c r="C79" s="24"/>
+    </row>
+    <row r="80" ht="14.5" spans="1:3">
       <c r="A80" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B80" s="23">
         <f>B78-B79</f>
         <v>9</v>
       </c>
-      <c r="C80" s="26"/>
-    </row>
-    <row r="81" ht="13.85" spans="1:2">
+      <c r="C80" s="24"/>
+    </row>
+    <row r="81" ht="14.5" spans="1:2">
       <c r="A81" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="4" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G76" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="3">
-      <filters>
-        <filter val="假"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="假"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/docs/public/exam/2019-shang-2.xlsx
+++ b/docs/public/exam/2019-shang-2.xlsx
@@ -1395,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
@@ -1422,7 +1422,7 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
     </row>
-    <row r="2" ht="15" hidden="1" spans="1:6">
+    <row r="2" ht="15" spans="1:6">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" ht="15" hidden="1" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1456,7 +1456,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" hidden="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:6">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" ht="15" hidden="1" spans="1:6">
+    <row r="5" ht="15" spans="1:6">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1489,7 +1489,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="15" hidden="1" spans="1:6">
+    <row r="6" s="2" customFormat="1" ht="15" spans="1:6">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1513,7 +1513,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
       <c r="D7" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(AND(B7="",C7=""),"假",IF(B7=C7,"真","假"))</f>
         <v>假</v>
       </c>
       <c r="E7" t="s">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" ht="15" hidden="1" spans="1:6">
+    <row r="8" ht="15" spans="1:6">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" ht="15" hidden="1" spans="1:6">
+    <row r="9" ht="15" spans="1:6">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" ht="15" hidden="1" spans="1:6">
+    <row r="10" ht="15" spans="1:6">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" ht="15" hidden="1" spans="1:6">
+    <row r="11" ht="15" spans="1:6">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" ht="15" hidden="1" spans="1:6">
+    <row r="12" ht="15" spans="1:6">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" ht="15" hidden="1" spans="1:6">
+    <row r="13" ht="15" spans="1:6">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" s="3" customFormat="1" ht="15" hidden="1" spans="1:6">
+    <row r="14" s="3" customFormat="1" ht="15" spans="1:6">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" s="3" customFormat="1" ht="15" hidden="1" spans="1:6">
+    <row r="15" s="3" customFormat="1" ht="15" spans="1:6">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" ht="15" hidden="1" spans="1:6">
+    <row r="16" ht="15" spans="1:6">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" ht="15" hidden="1" spans="1:6">
+    <row r="17" ht="15" spans="1:6">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" ht="15" hidden="1" spans="1:6">
+    <row r="18" ht="15" spans="1:6">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" ht="15" hidden="1" spans="1:6">
+    <row r="19" ht="15" spans="1:6">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -1722,7 +1722,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" ht="15" hidden="1" spans="1:6">
+    <row r="20" ht="15" spans="1:6">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" ht="15" hidden="1" spans="1:6">
+    <row r="21" ht="15" spans="1:6">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -1756,7 +1756,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" ht="15" hidden="1" spans="1:6">
+    <row r="22" ht="15" spans="1:6">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F22" s="19"/>
     </row>
-    <row r="23" ht="15" hidden="1" spans="1:7">
+    <row r="23" ht="15" spans="1:7">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -1789,7 +1789,7 @@
       <c r="F23" s="19"/>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" ht="15" hidden="1" spans="1:7">
+    <row r="24" ht="15" spans="1:7">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="F24" s="19"/>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" ht="15" hidden="1" spans="1:7">
+    <row r="25" ht="15" spans="1:7">
       <c r="A25" s="13">
         <v>24</v>
       </c>
@@ -1823,7 +1823,7 @@
       <c r="F25" s="19"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" ht="15" hidden="1" spans="1:6">
+    <row r="26" ht="15" spans="1:6">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" ht="15" hidden="1" spans="1:6">
+    <row r="27" ht="15" spans="1:6">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" ht="15" hidden="1" spans="1:6">
+    <row r="28" ht="15" spans="1:6">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F28" s="19"/>
     </row>
-    <row r="29" ht="15" hidden="1" spans="1:6">
+    <row r="29" ht="15" spans="1:6">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -1905,7 +1905,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" ht="15" hidden="1" spans="1:6">
+    <row r="31" ht="15" spans="1:6">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" ht="15" hidden="1" spans="1:6">
+    <row r="33" ht="15" spans="1:6">
       <c r="A33" s="13">
         <v>32</v>
       </c>
@@ -1956,7 +1956,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" ht="15" hidden="1" spans="1:6">
+    <row r="34" ht="15" spans="1:6">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" ht="15" hidden="1" spans="1:6">
+    <row r="35" ht="15" spans="1:6">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" ht="15" hidden="1" spans="1:6">
+    <row r="36" ht="15" spans="1:6">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" ht="15" hidden="1" spans="1:6">
+    <row r="37" ht="15" spans="1:6">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" ht="15" hidden="1" spans="1:6">
+    <row r="38" ht="15" spans="1:6">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" ht="15" hidden="1" spans="1:6">
+    <row r="39" ht="15" spans="1:6">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" ht="15" hidden="1" spans="1:6">
+    <row r="40" ht="15" spans="1:6">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" ht="15" hidden="1" spans="1:6">
+    <row r="41" ht="15" spans="1:6">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" ht="15" hidden="1" spans="1:6">
+    <row r="43" ht="15" spans="1:6">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" ht="15" hidden="1" spans="1:6">
+    <row r="44" ht="15" spans="1:6">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" ht="15" hidden="1" spans="1:6">
+    <row r="45" ht="15" spans="1:6">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -2175,7 +2175,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" ht="15" hidden="1" spans="1:6">
+    <row r="47" ht="15" spans="1:6">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
     </row>
-    <row r="48" ht="15" hidden="1" spans="1:6">
+    <row r="48" ht="15" spans="1:6">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" ht="15" hidden="1" spans="1:6">
+    <row r="49" ht="15" spans="1:6">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" ht="15" hidden="1" spans="1:6">
+    <row r="50" ht="15" spans="1:6">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
     </row>
-    <row r="68" s="2" customFormat="1" ht="15" hidden="1" spans="1:6">
+    <row r="68" s="2" customFormat="1" ht="15" spans="1:6">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -2491,7 +2491,7 @@
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
     </row>
-    <row r="69" ht="15" hidden="1" spans="1:6">
+    <row r="69" ht="15" spans="1:6">
       <c r="A69" s="13">
         <v>68</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
     </row>
-    <row r="70" ht="15" hidden="1" spans="1:6">
+    <row r="70" ht="15" spans="1:6">
       <c r="A70" s="13">
         <v>69</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
     </row>
-    <row r="71" ht="15" hidden="1" spans="1:6">
+    <row r="71" ht="15" spans="1:6">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -2645,14 +2645,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G76" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="equal" val="假"/>
-      </customFilters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
